--- a/ig/updateWorkflow/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/updateWorkflow/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-14T18:13:00+00:00</t>
+    <t>2024-02-14T18:23:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/updateWorkflow/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/updateWorkflow/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-14T18:23:24+00:00</t>
+    <t>2024-02-15T14:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/updateWorkflow/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/updateWorkflow/ValueSet-JDV-cipucd-all.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T14:01:02+00:00</t>
+    <t>2024-02-15T15:44:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t>No display for ContactDetail</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>FRANCE</t>
   </si>
   <si>
     <t>Description</t>
@@ -233,7 +239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -328,20 +334,28 @@
       <c r="A12" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>21</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>23</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -360,28 +374,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/ig/updateWorkflow/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/updateWorkflow/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T15:44:06+00:00</t>
+    <t>2024-02-15T16:22:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
